--- a/src/data/COREP_files/G_EU_C_C0400.xlsx
+++ b/src/data/COREP_files/G_EU_C_C0400.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -478,6 +478,9 @@
           <t>Total deferred tax assets</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -485,10 +488,6 @@
           <t>020</t>
         </is>
       </c>
-      <c r="C7">
-        <f>C$6&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Deferred tax assets that do not rely on future profitability</t>
@@ -498,6 +497,9 @@
         <is>
           <t>Article 36 of CRR</t>
         </is>
+      </c>
+      <c r="F7" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -506,10 +508,6 @@
           <t>030</t>
         </is>
       </c>
-      <c r="C8">
-        <f>C$6&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Deferred tax assets that rely on future profitability and do not arise from temporary differences</t>
@@ -527,10 +525,6 @@
           <t>040</t>
         </is>
       </c>
-      <c r="C9">
-        <f>C$6&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Deferred tax assets that rely on future profitability and arise from temporary differences</t>
@@ -540,6 +534,9 @@
         <is>
           <t>Articles 33(1) point (c); 35 and 45(1) point (a) of CRR</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +560,6 @@
           <t>060</t>
         </is>
       </c>
-      <c r="C11">
-        <f>C$10&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Deferred tax liabilities non deductible from deferred tax assets that rely on future profitability</t>
@@ -584,10 +577,6 @@
           <t>070</t>
         </is>
       </c>
-      <c r="C12">
-        <f>C$10&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Deferred tax liabilities deductible from deferred tax assets that rely on future profitability</t>
@@ -605,10 +594,6 @@
           <t>080</t>
         </is>
       </c>
-      <c r="C13">
-        <f>C$12&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Deductible deferred tax liabilities associated with deferred tax assets that rely on future profitability and do not arise from temporary differences</t>
@@ -626,10 +611,6 @@
           <t>090</t>
         </is>
       </c>
-      <c r="C14">
-        <f>C$12&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Deductible deferred tax liabilities associated with deferred tax assets that rely on future profitability and arise from temporary differences</t>
@@ -639,6 +620,9 @@
         <is>
           <t>Article 35(3), (4) and (5) of CRR</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -674,10 +658,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C17">
-        <f>C$16&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Total credit risk adjustments, additional value adjustments and other own funds reductions eligible for inclusion in the calculation of the expected loss amount</t>
@@ -695,10 +675,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C18">
-        <f>C$17&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>General credit risk adjustments</t>
@@ -716,10 +692,6 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C19">
-        <f>C$17&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Specific credit risk adjustments</t>
@@ -737,10 +709,6 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C20">
-        <f>C$17&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Additional value adjustments and other own funds reductions</t>
@@ -758,10 +726,6 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C21">
-        <f>C$16&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">Total expected losses eligible </t>
@@ -799,10 +763,6 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C23">
-        <f>C$22&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Specific credit risk adjustments and positions treated similarily</t>
@@ -812,6 +772,9 @@
         <is>
           <t>Article 155 of CRR</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -820,10 +783,6 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C24">
-        <f>C$22&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Total expected losses eligible </t>
@@ -893,6 +852,9 @@
         <is>
           <t>Article 59 point (c) of CRR</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="28">
@@ -937,6 +899,9 @@
           <t>Article 45(1) points (a) and (b) of CRR</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -1003,10 +968,6 @@
       <c r="B35" t="n">
         <v>240</v>
       </c>
-      <c r="C35">
-        <f>C34&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Direct holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1022,10 +983,6 @@
       <c r="B36" t="n">
         <v>250</v>
       </c>
-      <c r="C36">
-        <f>C35&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Gross direct holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1041,10 +998,6 @@
       <c r="B37" t="n">
         <v>260</v>
       </c>
-      <c r="C37">
-        <f>C35&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -1060,10 +1013,6 @@
       <c r="B38" t="n">
         <v>270</v>
       </c>
-      <c r="C38">
-        <f>C34&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Indirect holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1079,10 +1028,6 @@
       <c r="B39" t="n">
         <v>280</v>
       </c>
-      <c r="C39">
-        <f>C38&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Gross indirect holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1098,10 +1043,6 @@
       <c r="B40" t="n">
         <v>290</v>
       </c>
-      <c r="C40">
-        <f>C38&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -1119,10 +1060,6 @@
           <t>291</t>
         </is>
       </c>
-      <c r="C41">
-        <f>C34&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>Synthetic holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1140,10 +1077,6 @@
           <t>292</t>
         </is>
       </c>
-      <c r="C42">
-        <f>C41&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of CET1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1160,10 +1093,6 @@
         <is>
           <t>293</t>
         </is>
-      </c>
-      <c r="C43">
-        <f>C41&amp;".2"</f>
-        <v/>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1193,15 +1122,14 @@
           <t>Articles 55 to 57 of CRR</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
         <v>310</v>
       </c>
-      <c r="C45">
-        <f>C44&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Direct holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1217,10 +1145,6 @@
       <c r="B46" t="n">
         <v>320</v>
       </c>
-      <c r="C46">
-        <f>C45&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>Gross direct holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1236,10 +1160,6 @@
       <c r="B47" t="n">
         <v>330</v>
       </c>
-      <c r="C47">
-        <f>C45&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -1249,16 +1169,15 @@
         <is>
           <t>Article 56 of CRR</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
         <v>340</v>
       </c>
-      <c r="C48">
-        <f>C44&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Indirect holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1268,16 +1187,15 @@
         <is>
           <t>Articles 22(17), 55 and 56 of CRR</t>
         </is>
+      </c>
+      <c r="F48" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
         <v>350</v>
       </c>
-      <c r="C49">
-        <f>C48&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Gross indirect holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1287,16 +1205,15 @@
         <is>
           <t>Articles 22(17), 55 and 56 of CRR</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
         <v>360</v>
       </c>
-      <c r="C50">
-        <f>C48&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -1314,10 +1231,6 @@
           <t>361</t>
         </is>
       </c>
-      <c r="C51">
-        <f>C44&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>Synthetic holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1335,10 +1248,6 @@
           <t>362</t>
         </is>
       </c>
-      <c r="C52">
-        <f>C51&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of AT1 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1355,10 +1264,6 @@
         <is>
           <t>363</t>
         </is>
-      </c>
-      <c r="C53">
-        <f>C51&amp;".2"</f>
-        <v/>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1388,15 +1293,14 @@
           <t>Articles 65 to 67 of CRR</t>
         </is>
       </c>
+      <c r="F54" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
         <v>380</v>
       </c>
-      <c r="C55">
-        <f>C54&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>Direct holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1412,10 +1316,6 @@
       <c r="B56" t="n">
         <v>390</v>
       </c>
-      <c r="C56">
-        <f>C55&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Gross direct holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1431,10 +1331,6 @@
       <c r="B57" t="n">
         <v>400</v>
       </c>
-      <c r="C57">
-        <f>C55&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -1450,10 +1346,6 @@
       <c r="B58" t="n">
         <v>410</v>
       </c>
-      <c r="C58">
-        <f>C54&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Indirect holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1469,10 +1361,6 @@
       <c r="B59" t="n">
         <v>420</v>
       </c>
-      <c r="C59">
-        <f>C58&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Gross indirect holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1488,10 +1376,6 @@
       <c r="B60" t="n">
         <v>430</v>
       </c>
-      <c r="C60">
-        <f>C58&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -1509,10 +1393,6 @@
           <t>431</t>
         </is>
       </c>
-      <c r="C61">
-        <f>C54&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Synthetic holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1530,10 +1410,6 @@
           <t>432</t>
         </is>
       </c>
-      <c r="C62">
-        <f>C61&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of T2 capital of financial sector entities where the institution does not have a significant investment</t>
@@ -1550,10 +1426,6 @@
         <is>
           <t>433</t>
         </is>
-      </c>
-      <c r="C63">
-        <f>C61&amp;".2"</f>
-        <v/>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1595,10 +1467,6 @@
       <c r="B66" t="n">
         <v>450</v>
       </c>
-      <c r="C66">
-        <f>C65&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Direct holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1614,10 +1482,6 @@
       <c r="B67" t="n">
         <v>460</v>
       </c>
-      <c r="C67">
-        <f>C66&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Gross direct holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1633,10 +1497,6 @@
       <c r="B68" t="n">
         <v>470</v>
       </c>
-      <c r="C68">
-        <f>C66&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -1652,10 +1512,6 @@
       <c r="B69" t="n">
         <v>480</v>
       </c>
-      <c r="C69">
-        <f>C65&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>Indirect holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1671,10 +1527,6 @@
       <c r="B70" t="n">
         <v>490</v>
       </c>
-      <c r="C70">
-        <f>C69&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Gross indirect holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1684,16 +1536,15 @@
         <is>
           <t>Articles 22(17), 41 and 42 of CRR</t>
         </is>
+      </c>
+      <c r="F70" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
         <v>500</v>
       </c>
-      <c r="C71">
-        <f>C69&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -1711,10 +1562,6 @@
           <t>501</t>
         </is>
       </c>
-      <c r="C72">
-        <f>C65&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>Synthetic holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1732,10 +1579,6 @@
           <t>502</t>
         </is>
       </c>
-      <c r="C73">
-        <f>C72&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of CET1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1752,10 +1595,6 @@
         <is>
           <t>503</t>
         </is>
-      </c>
-      <c r="C74">
-        <f>C72&amp;".2"</f>
-        <v/>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1790,10 +1629,6 @@
       <c r="B76" t="n">
         <v>520</v>
       </c>
-      <c r="C76">
-        <f>C75&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Direct holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1809,10 +1644,6 @@
       <c r="B77" t="n">
         <v>530</v>
       </c>
-      <c r="C77">
-        <f>C76&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Gross direct holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1828,10 +1659,6 @@
       <c r="B78" t="n">
         <v>540</v>
       </c>
-      <c r="C78">
-        <f>C76&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -1847,10 +1674,6 @@
       <c r="B79" t="n">
         <v>550</v>
       </c>
-      <c r="C79">
-        <f>C75&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>Indirect holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1866,10 +1689,6 @@
       <c r="B80" t="n">
         <v>560</v>
       </c>
-      <c r="C80">
-        <f>C79&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Gross indirect holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1885,10 +1704,6 @@
       <c r="B81" t="n">
         <v>570</v>
       </c>
-      <c r="C81">
-        <f>C79&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -1906,10 +1721,6 @@
           <t>571</t>
         </is>
       </c>
-      <c r="C82">
-        <f>C75&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Synthetic holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1927,10 +1738,6 @@
           <t>572</t>
         </is>
       </c>
-      <c r="C83">
-        <f>C82&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of AT1 capital of financial sector entities where the institution has a significant investment</t>
@@ -1947,10 +1754,6 @@
         <is>
           <t>573</t>
         </is>
-      </c>
-      <c r="C84">
-        <f>C82&amp;".2"</f>
-        <v/>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -1985,10 +1788,6 @@
       <c r="B86" t="n">
         <v>590</v>
       </c>
-      <c r="C86">
-        <f>C85&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Direct holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2004,10 +1803,6 @@
       <c r="B87" t="n">
         <v>600</v>
       </c>
-      <c r="C87">
-        <f>C86&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>Gross direct holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2023,10 +1818,6 @@
       <c r="B88" t="n">
         <v>610</v>
       </c>
-      <c r="C88">
-        <f>C86&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the direct gross holdings included above</t>
@@ -2042,10 +1833,6 @@
       <c r="B89" t="n">
         <v>620</v>
       </c>
-      <c r="C89">
-        <f>C85&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Indirect holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2061,10 +1848,6 @@
       <c r="B90" t="n">
         <v>630</v>
       </c>
-      <c r="C90">
-        <f>C89&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Gross indirect holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2080,10 +1863,6 @@
       <c r="B91" t="n">
         <v>640</v>
       </c>
-      <c r="C91">
-        <f>C89&amp;".2"</f>
-        <v/>
-      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>(-) Permitted offsetting short positions in relation to the indirect gross holdings included above</t>
@@ -2101,10 +1880,6 @@
           <t>641</t>
         </is>
       </c>
-      <c r="C92">
-        <f>C85&amp;".3"</f>
-        <v/>
-      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>Synthetic holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2122,10 +1897,6 @@
           <t>642</t>
         </is>
       </c>
-      <c r="C93">
-        <f>C92&amp;".1"</f>
-        <v/>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Gross synthetic holdings of T2 capital of financial sector entities where the institution has a significant investment</t>
@@ -2142,10 +1913,6 @@
         <is>
           <t>643</t>
         </is>
-      </c>
-      <c r="C94">
-        <f>C92&amp;".2"</f>
-        <v/>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2358,6 +2125,9 @@
           <t>Article 122 point (2) of CRD</t>
         </is>
       </c>
+      <c r="F107" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
@@ -2447,6 +2217,9 @@
         <is>
           <t>Article 131 of CRD</t>
         </is>
+      </c>
+      <c r="F113" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="114">
